--- a/data/trans_dic/P1801_2016_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1801_2016_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,56; 31,51</t>
+          <t>22,37; 30,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,3; 29,28</t>
+          <t>13,37; 25,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,43; 45,59</t>
+          <t>36,14; 46,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,0; 48,07</t>
+          <t>33,56; 47,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,03; 36,74</t>
+          <t>30,03; 36,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,55; 35,01</t>
+          <t>24,42; 33,88</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,33; 33,95</t>
+          <t>26,85; 34,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,8</t>
+          <t>28,36; 39,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,2; 53,3</t>
+          <t>45,03; 53,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 44,74</t>
+          <t>36,96; 46,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,83; 42,56</t>
+          <t>36,92; 42,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 40,64</t>
+          <t>34,04; 41,62</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,92; 45,67</t>
+          <t>38,27; 45,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 47,93</t>
+          <t>37,28; 45,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,24; 56,12</t>
+          <t>48,5; 56,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44,13; 51,11</t>
+          <t>44,51; 51,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,23; 49,85</t>
+          <t>44,39; 49,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,1; 48,7</t>
+          <t>41,64; 47,06</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,43; 52,45</t>
+          <t>43,91; 52,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,36; 85,57</t>
+          <t>48,31; 55,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,88; 55,98</t>
+          <t>48,03; 55,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,71; 58,53</t>
+          <t>53,63; 59,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,21; 53,26</t>
+          <t>47,14; 53,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,94; 76,91</t>
+          <t>52,06; 56,91</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,23; 62,4</t>
+          <t>53,15; 62,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,66; 61,83</t>
+          <t>52,79; 60,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,08; 70,47</t>
+          <t>61,88; 71,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,8; 66,83</t>
+          <t>61,48; 67,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,84; 65,48</t>
+          <t>58,65; 65,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,22; 63,59</t>
+          <t>58,27; 63,02</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,51; 73,18</t>
+          <t>62,23; 72,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,76; 68,44</t>
+          <t>60,85; 68,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,27; 80,38</t>
+          <t>70,55; 79,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,47; 91,09</t>
+          <t>63,56; 70,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,33; 75,43</t>
+          <t>68,34; 75,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,09; 85,68</t>
+          <t>63,05; 68,33</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,57; 80,07</t>
+          <t>70,91; 80,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,11; 77,98</t>
+          <t>68,3; 77,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66,23; 77,17</t>
+          <t>66,43; 76,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,66; 73,94</t>
+          <t>67,8; 74,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,67; 76,7</t>
+          <t>69,41; 76,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,17; 74,63</t>
+          <t>69,59; 74,45</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,71; 48,26</t>
+          <t>44,91; 48,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,68; 64,44</t>
+          <t>46,08; 49,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,48; 58,78</t>
+          <t>55,38; 58,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53,4; 64,75</t>
+          <t>54,36; 57,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,62; 53,11</t>
+          <t>50,81; 53,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,85; 61,18</t>
+          <t>50,92; 53,3</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>76541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127197</t>
+          <t>146401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>212500</t>
+          <t>222942</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94647; 132153</t>
+          <t>93840; 129939</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57183; 117111</t>
+          <t>54506; 104568</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140226; 180427</t>
+          <t>143024; 182536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106435; 150463</t>
+          <t>121093; 171944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>244804; 299473</t>
+          <t>244803; 299736</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>175073; 249649</t>
+          <t>187733; 260442</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146652</t>
+          <t>162004</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190446</t>
+          <t>208576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>337098</t>
+          <t>370580</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155460; 200496</t>
+          <t>158520; 202843</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>122194; 172824</t>
+          <t>135251; 190468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254701; 300397</t>
+          <t>253774; 301325</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119305; 228426</t>
+          <t>184894; 232171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>425079; 491125</t>
+          <t>426075; 490718</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>255861; 379672</t>
+          <t>332647; 406656</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>233496</t>
+          <t>255022</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259564</t>
+          <t>297277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>493060</t>
+          <t>552299</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>253723; 305552</t>
+          <t>256084; 306821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>209357; 256454</t>
+          <t>231028; 281716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319057; 371180</t>
+          <t>320800; 371162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239117; 276902</t>
+          <t>276623; 319558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>588508; 663208</t>
+          <t>590633; 661660</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>464080; 524398</t>
+          <t>516798; 584079</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>589579</t>
+          <t>363770</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>386843</t>
+          <t>417529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>976423</t>
+          <t>781299</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>287057; 338843</t>
+          <t>283664; 338225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>464298; 758791</t>
+          <t>337958; 388485</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310805; 363324</t>
+          <t>311776; 363118</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>325250; 416475</t>
+          <t>394469; 439039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>611455; 689822</t>
+          <t>610484; 688492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>846211; 1229204</t>
+          <t>747073; 816654</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>324262</t>
+          <t>345188</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349035</t>
+          <t>390847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>673297</t>
+          <t>736035</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>254395; 298243</t>
+          <t>254006; 298054</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>300612; 346379</t>
+          <t>321105; 369255</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>308439; 350108</t>
+          <t>307425; 353336</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>332327; 365297</t>
+          <t>373473; 408589</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>573580; 638298</t>
+          <t>571678; 637852</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>644367; 703794</t>
+          <t>708403; 766155</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239096</t>
+          <t>262520</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>473547</t>
+          <t>293417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>712643</t>
+          <t>555937</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>208993; 244647</t>
+          <t>208045; 242862</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>223688; 251961</t>
+          <t>247706; 280327</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269249; 303628</t>
+          <t>266494; 302161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>398028; 553819</t>
+          <t>278854; 308036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>486545; 537142</t>
+          <t>486665; 534071</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>635323; 836325</t>
+          <t>533271; 577915</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>208433</t>
+          <t>226615</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>301622</t>
+          <t>330518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>510055</t>
+          <t>557133</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>181364; 205769</t>
+          <t>182225; 206098</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>195401; 220491</t>
+          <t>211881; 239264</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>265038; 308824</t>
+          <t>265821; 305412</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>287382; 314042</t>
+          <t>314251; 343377</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>457817; 504079</t>
+          <t>456155; 504362</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>489406; 528048</t>
+          <t>538368; 576014</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1517483; 1638137</t>
+          <t>1524395; 1638978</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1682575; 2227435</t>
+          <t>1626326; 1757140</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1966592; 2083332</t>
+          <t>1962823; 2088270</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1952295; 2367460</t>
+          <t>2026244; 2136118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3512610; 3685006</t>
+          <t>3525518; 3700078</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3688333; 4351924</t>
+          <t>3695188; 3868475</t>
         </is>
       </c>
     </row>
